--- a/Homework2/my-simulation/question7.xlsx
+++ b/Homework2/my-simulation/question7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD4C922-0925-4C67-AF61-8B75B198DD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBBF57B-AFB5-458B-BF4A-BD9348BC8BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2724B8F-81E9-4CBD-8F1B-A41AC1296333}"/>
   </bookViews>
@@ -92,8 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -467,14 +466,14 @@
         <f>B2-C2</f>
         <v>2.8057829740135709E-8</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1">
-        <f>MIN($D:$D)</f>
-        <v>-2.9118879475431569E-6</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2">
+        <f>MAX($D:$D)</f>
+        <v>2.8057829740135709E-8</v>
+      </c>
+      <c r="I2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -493,14 +492,14 @@
         <f t="shared" ref="D3:D66" si="1">B3-C3</f>
         <v>-5.2560556323966168E-9</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="1">
-        <f>MAX($D:$D)</f>
-        <v>2.8057829740135709E-8</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3">
+        <f>MIN($D:$D)</f>
+        <v>-2.9118879475431569E-6</v>
+      </c>
+      <c r="I3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Homework2/my-simulation/question7.xlsx
+++ b/Homework2/my-simulation/question7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBBF57B-AFB5-458B-BF4A-BD9348BC8BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE648C32-4901-4B8D-B4F7-325E999963D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2724B8F-81E9-4CBD-8F1B-A41AC1296333}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>X--Trace 1::[V(vo)]</t>
   </si>
@@ -53,17 +53,49 @@
     <t>MAX Delta V</t>
   </si>
   <si>
-    <t>V</t>
+    <t>MIN Delta V</t>
   </si>
   <si>
-    <t>MIN Delta V</t>
+    <t>Error_input</t>
+  </si>
+  <si>
+    <t>Error_output</t>
+  </si>
+  <si>
+    <t>Max Error Input</t>
+  </si>
+  <si>
+    <t>Min Error Input</t>
+  </si>
+  <si>
+    <t>Max Error Output</t>
+  </si>
+  <si>
+    <t>Min Error Output</t>
+  </si>
+  <si>
+    <t>MAX V_o</t>
+  </si>
+  <si>
+    <t>MIN V_o</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000%"/>
+    <numFmt numFmtId="165" formatCode="0.00000%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,14 +121,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,16 +464,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67EEACAA-FEE5-48D9-B306-0374D5937AC0}">
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,8 +490,14 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1E-3</v>
       </c>
@@ -466,18 +512,23 @@
         <f>B2-C2</f>
         <v>2.8057829740135709E-8</v>
       </c>
+      <c r="E2" s="1">
+        <f>(B2/100-A2)/A2</f>
+        <v>2.80578297357989E-7</v>
+      </c>
+      <c r="F2" s="1">
+        <f>(B2-C2)/C2</f>
+        <v>2.8057829740135709E-7</v>
+      </c>
       <c r="G2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <f>MAX($D:$D)</f>
-        <v>2.8057829740135709E-8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2">
+        <f>MAX($E:$E)</f>
+        <v>2.80578297357989E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1.1000000000000001E-3</v>
       </c>
@@ -492,18 +543,23 @@
         <f t="shared" ref="D3:D66" si="1">B3-C3</f>
         <v>-5.2560556323966168E-9</v>
       </c>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E66" si="2">(B3/100-A3)/A3</f>
+        <v>-4.7782323986074078E-8</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F66" si="3">(B3-C3)/C3</f>
+        <v>-4.7782323930878334E-8</v>
+      </c>
       <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <f>MIN($D:$D)</f>
-        <v>-2.9118879475431569E-6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2">
+        <f>MIN($E:$E)</f>
+        <v>-2.9713142320736078E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1.2000000000000001E-3</v>
       </c>
@@ -518,8 +574,16 @@
         <f t="shared" si="1"/>
         <v>-3.8665620941125134E-8</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E4" s="1">
+        <f t="shared" si="2"/>
+        <v>-3.2221350786439346E-7</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="3"/>
+        <v>-3.2221350784270941E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1.3000000000000002E-3</v>
       </c>
@@ -534,8 +598,23 @@
         <f t="shared" si="1"/>
         <v>-7.2075181711817038E-8</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E5" s="1">
+        <f t="shared" si="2"/>
+        <v>-5.5442447474631691E-7</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="3"/>
+        <v>-5.5442447470628486E-7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2">
+        <f>MAX($F:$F)</f>
+        <v>2.8057829740135709E-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1.4000000000000002E-3</v>
       </c>
@@ -550,8 +629,23 @@
         <f t="shared" si="1"/>
         <v>-1.054847435510986E-7</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E6" s="1">
+        <f t="shared" si="2"/>
+        <v>-7.5346245394880938E-7</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="3"/>
+        <v>-7.5346245393641856E-7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2">
+        <f>MIN($F:$F)</f>
+        <v>-2.9713142321868959E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1.5000000000000002E-3</v>
       </c>
@@ -566,8 +660,16 @@
         <f t="shared" si="1"/>
         <v>-1.3889430813818215E-7</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E7" s="1">
+        <f t="shared" si="2"/>
+        <v>-9.2596205428345958E-7</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="3"/>
+        <v>-9.2596205425454759E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1.6000000000000003E-3</v>
       </c>
@@ -582,8 +684,23 @@
         <f t="shared" si="1"/>
         <v>-1.7230386695210598E-7</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E8" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.076899168391031E-6</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.0768991684506621E-6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <f>MAX(D2:D202)</f>
+        <v>2.8057829740135709E-8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1.7000000000000003E-3</v>
       </c>
@@ -598,8 +715,23 @@
         <f t="shared" si="1"/>
         <v>-2.0571343065101111E-7</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E9" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.2100790037835578E-6</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.2100790038294767E-6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <f>MIN(D2:D202)</f>
+        <v>-2.9118879475431569E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1.8000000000000004E-3</v>
       </c>
@@ -614,8 +746,16 @@
         <f t="shared" si="1"/>
         <v>-2.391229914355808E-7</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E10" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.3284610634249932E-6</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.3284610635310041E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1.9000000000000004E-3</v>
       </c>
@@ -630,8 +770,23 @@
         <f t="shared" si="1"/>
         <v>-2.7253255333037352E-7</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E11" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.4343818596791952E-6</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.4343818596335446E-6</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <f>MAX($B$2:$B$202)</f>
+        <v>0.97999708811205211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2.0000000000000005E-3</v>
       </c>
@@ -646,8 +801,23 @@
         <f t="shared" si="1"/>
         <v>-3.0594211600232235E-7</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E12" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.5297105799942641E-6</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.5297105800116115E-6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <f>MIN($B$2:$B$202)</f>
+        <v>0.10000002805782975</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2.1000000000000003E-3</v>
       </c>
@@ -662,8 +832,16 @@
         <f t="shared" si="1"/>
         <v>-3.3935167687015877E-7</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E13" s="1">
+        <f>(B13/100-A13)/A13</f>
+        <v>-1.6159603660979385E-6</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.615960366048375E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2.2000000000000001E-3</v>
       </c>
@@ -678,8 +856,16 @@
         <f t="shared" si="1"/>
         <v>-3.7276123679430562E-7</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E14" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.6943692582190153E-6</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.6943692581559346E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2.3E-3</v>
       </c>
@@ -694,8 +880,16 @@
         <f t="shared" si="1"/>
         <v>-4.0617079946625445E-7</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E15" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.7659599976869096E-6</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.7659599976793674E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2.3999999999999998E-3</v>
       </c>
@@ -710,8 +904,16 @@
         <f t="shared" si="1"/>
         <v>-4.3958036133329159E-7</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.8315848387658389E-6</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.831584838888715E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2.4999999999999996E-3</v>
       </c>
@@ -726,8 +928,16 @@
         <f t="shared" si="1"/>
         <v>-4.729899251709746E-7</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.8919597007116542E-6</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.8919597006838986E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2.5999999999999994E-3</v>
       </c>
@@ -742,8 +952,16 @@
         <f t="shared" si="1"/>
         <v>-5.0639948501185472E-7</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.9476903269953605E-6</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.9476903269686722E-6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2.6999999999999993E-3</v>
       </c>
@@ -758,8 +976,16 @@
         <f t="shared" si="1"/>
         <v>-5.3980904690664744E-7</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.9992927664494148E-6</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="3"/>
+        <v>-1.9992927663209169E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2.7999999999999991E-3</v>
       </c>
@@ -774,8 +1000,16 @@
         <f t="shared" si="1"/>
         <v>-5.7321860996717433E-7</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.0472093212431877E-6</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.0472093213113374E-6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2.8999999999999989E-3</v>
       </c>
@@ -790,8 +1024,16 @@
         <f t="shared" si="1"/>
         <v>-6.0662817080725517E-7</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.0918212787234719E-6</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.0918212786457084E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2.9999999999999988E-3</v>
       </c>
@@ -806,8 +1048,16 @@
         <f t="shared" si="1"/>
         <v>-6.4003773059262414E-7</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.1334591019465027E-6</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.1334591019754145E-6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3.0999999999999986E-3</v>
       </c>
@@ -822,8 +1072,16 @@
         <f t="shared" si="1"/>
         <v>-6.7344729265395031E-7</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.1724106215482951E-6</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.1724106214643571E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3.1999999999999984E-3</v>
       </c>
@@ -838,8 +1096,16 @@
         <f t="shared" si="1"/>
         <v>-7.0685685543692145E-7</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.2089276732078547E-6</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.2089276732403808E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>3.2999999999999982E-3</v>
       </c>
@@ -854,8 +1120,16 @@
         <f t="shared" si="1"/>
         <v>-7.4026641722069186E-7</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.2432315671987561E-6</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.2432315673354308E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>3.3999999999999981E-3</v>
       </c>
@@ -870,8 +1144,16 @@
         <f t="shared" si="1"/>
         <v>-7.736759802257076E-7</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.2755175888991415E-6</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.2755175888991415E-6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3.4999999999999979E-3</v>
       </c>
@@ -886,8 +1168,16 @@
         <f t="shared" si="1"/>
         <v>-8.0708554128783305E-7</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.3059586893739845E-6</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.3059586893938102E-6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>3.5999999999999977E-3</v>
       </c>
@@ -902,8 +1192,16 @@
         <f t="shared" si="1"/>
         <v>-8.4049510323813692E-7</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.3347086201300308E-6</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.3347086201059373E-6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3.6999999999999976E-3</v>
       </c>
@@ -918,8 +1216,16 @@
         <f t="shared" si="1"/>
         <v>-8.7390466418924007E-7</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.3619044977618743E-6</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.3619044978087584E-6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3.7999999999999974E-3</v>
       </c>
@@ -934,8 +1240,16 @@
         <f t="shared" si="1"/>
         <v>-9.073142270832335E-7</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.3876690186629152E-6</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.3876690186400898E-6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3.8999999999999972E-3</v>
       </c>
@@ -950,8 +1264,16 @@
         <f t="shared" si="1"/>
         <v>-9.4072378892251507E-7</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.412112279301846E-6</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.4121122792885019E-6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3.9999999999999975E-3</v>
       </c>
@@ -966,8 +1288,16 @@
         <f t="shared" si="1"/>
         <v>-9.7413335092833009E-7</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.4353333772340907E-6</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.4353333773208269E-6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4.0999999999999977E-3</v>
       </c>
@@ -982,8 +1312,16 @@
         <f t="shared" si="1"/>
         <v>-1.0075429111022771E-6</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.4574217343450268E-6</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.4574217343957993E-6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>4.199999999999998E-3</v>
       </c>
@@ -998,8 +1336,16 @@
         <f t="shared" si="1"/>
         <v>-1.0409524741072929E-6</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.478458271741856E-6</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.4784582716840316E-6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>4.2999999999999983E-3</v>
       </c>
@@ -1014,8 +1360,16 @@
         <f t="shared" si="1"/>
         <v>-1.0743620349473737E-6</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.4985163602943197E-6</v>
+      </c>
+      <c r="F35" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.4985163603427306E-6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>4.3999999999999985E-3</v>
       </c>
@@ -1030,8 +1384,16 @@
         <f t="shared" si="1"/>
         <v>-1.107771598896079E-6</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.5176627248426677E-6</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.517662724763817E-6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4.4999999999999988E-3</v>
       </c>
@@ -1046,8 +1408,16 @@
         <f t="shared" si="1"/>
         <v>-1.1411811591810483E-6</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.5359581313746636E-6</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.5359581315134415E-6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>4.5999999999999991E-3</v>
       </c>
@@ -1062,8 +1432,16 @@
         <f t="shared" si="1"/>
         <v>-1.1745907231852648E-6</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.5534580939338069E-6</v>
+      </c>
+      <c r="F38" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.5534580938810109E-6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>4.6999999999999993E-3</v>
       </c>
@@ -1078,8 +1456,16 @@
         <f t="shared" si="1"/>
         <v>-1.2080002814163215E-6</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.5702133646860511E-6</v>
+      </c>
+      <c r="F39" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.5702133647155783E-6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>4.7999999999999996E-3</v>
       </c>
@@ -1094,8 +1480,16 @@
         <f t="shared" si="1"/>
         <v>-1.2414098443658261E-6</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.5862705090954714E-6</v>
+      </c>
+      <c r="F40" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.5862705090954714E-6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4.8999999999999998E-3</v>
       </c>
@@ -1110,8 +1504,16 @@
         <f t="shared" si="1"/>
         <v>-1.2748194064826635E-6</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.6016722580854016E-6</v>
+      </c>
+      <c r="F41" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.6016722581278846E-6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -1126,8 +1528,16 @@
         <f t="shared" si="1"/>
         <v>-1.3082289705979022E-6</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.6164579412790712E-6</v>
+      </c>
+      <c r="F42" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.6164579411958044E-6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>5.1000000000000004E-3</v>
       </c>
@@ -1142,8 +1552,16 @@
         <f t="shared" si="1"/>
         <v>-1.3416385316045165E-6</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.630663787466639E-6</v>
+      </c>
+      <c r="F43" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.6306637874598361E-6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>5.2000000000000006E-3</v>
       </c>
@@ -1158,8 +1576,16 @@
         <f t="shared" si="1"/>
         <v>-1.3750480925001085E-6</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.644323254954685E-6</v>
+      </c>
+      <c r="F44" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.644323254807901E-6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>5.3000000000000009E-3</v>
       </c>
@@ -1174,8 +1600,16 @@
         <f t="shared" si="1"/>
         <v>-1.4084576541728566E-6</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.6574672719849807E-6</v>
+      </c>
+      <c r="F45" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.6574672720242572E-6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>5.4000000000000012E-3</v>
       </c>
@@ -1190,8 +1624,16 @@
         <f t="shared" si="1"/>
         <v>-1.4418672179550285E-6</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.6701244775852733E-6</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.6701244776944965E-6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>5.5000000000000014E-3</v>
       </c>
@@ -1206,8 +1648,16 @@
         <f t="shared" si="1"/>
         <v>-1.4752767779624421E-6</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.6823214143825456E-6</v>
+      </c>
+      <c r="F47" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.6823214144771668E-6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5.6000000000000017E-3</v>
       </c>
@@ -1222,8 +1672,16 @@
         <f t="shared" si="1"/>
         <v>-1.5086863415225693E-6</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.6940827527994139E-6</v>
+      </c>
+      <c r="F48" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.6940827527188729E-6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>5.7000000000000019E-3</v>
       </c>
@@ -1238,8 +1696,16 @@
         <f t="shared" si="1"/>
         <v>-1.5420959037504289E-6</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7054314100884711E-6</v>
+      </c>
+      <c r="F49" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.7054314100884711E-6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>5.8000000000000022E-3</v>
       </c>
@@ -1254,8 +1720,16 @@
         <f t="shared" si="1"/>
         <v>-1.5755054637578425E-6</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7163887306289325E-6</v>
+      </c>
+      <c r="F50" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.716388730616969E-6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5.9000000000000025E-3</v>
       </c>
@@ -1270,8 +1744,16 @@
         <f t="shared" si="1"/>
         <v>-1.6089150260967244E-6</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.726974620397074E-6</v>
+      </c>
+      <c r="F51" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.7269746205029213E-6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6.0000000000000027E-3</v>
       </c>
@@ -1286,8 +1768,16 @@
         <f t="shared" si="1"/>
         <v>-1.6423245869923164E-6</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7372076448599799E-6</v>
+      </c>
+      <c r="F52" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.7372076449871928E-6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>6.100000000000003E-3</v>
       </c>
@@ -1302,8 +1792,16 @@
         <f t="shared" si="1"/>
         <v>-1.6757341494422207E-6</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7471051630257203E-6</v>
+      </c>
+      <c r="F53" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.7471051630200325E-6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>6.2000000000000033E-3</v>
       </c>
@@ -1318,8 +1816,16 @@
         <f t="shared" si="1"/>
         <v>-1.7091437105598573E-6</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7566834041735678E-6</v>
+      </c>
+      <c r="F54" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.7566834041288004E-6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>6.3000000000000035E-3</v>
       </c>
@@ -1334,8 +1840,16 @@
         <f t="shared" si="1"/>
         <v>-1.7425532765624752E-6</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7659575818837464E-6</v>
+      </c>
+      <c r="F55" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.765957581845197E-6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>6.4000000000000038E-3</v>
       </c>
@@ -1350,8 +1864,16 @@
         <f t="shared" si="1"/>
         <v>-1.7759628379021564E-6</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7749419342221176E-6</v>
+      </c>
+      <c r="F56" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.7749419342221176E-6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>6.500000000000004E-3</v>
       </c>
@@ -1366,8 +1888,16 @@
         <f t="shared" si="1"/>
         <v>-1.8093723982426368E-6</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7836498434822345E-6</v>
+      </c>
+      <c r="F57" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.783649843450209E-6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>6.6000000000000043E-3</v>
       </c>
@@ -1382,8 +1912,16 @@
         <f t="shared" si="1"/>
         <v>-1.8427819603594742E-6</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.7920938792011164E-6</v>
+      </c>
+      <c r="F58" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.7920938793325348E-6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>6.7000000000000046E-3</v>
       </c>
@@ -1398,8 +1936,16 @@
         <f t="shared" si="1"/>
         <v>-1.8761915228093784E-6</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8002858549290124E-6</v>
+      </c>
+      <c r="F59" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.8002858549393687E-6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>6.8000000000000048E-3</v>
       </c>
@@ -1414,8 +1960,16 @@
         <f t="shared" si="1"/>
         <v>-1.9096010842600819E-6</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8082368886636847E-6</v>
+      </c>
+      <c r="F60" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.8082368886177653E-6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>6.9000000000000051E-3</v>
       </c>
@@ -1430,8 +1984,16 @@
         <f t="shared" si="1"/>
         <v>-1.9430106478202092E-6</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8159574606693348E-6</v>
+      </c>
+      <c r="F61" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.8159574606089969E-6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>7.0000000000000053E-3</v>
       </c>
@@ -1446,8 +2008,16 @@
         <f t="shared" si="1"/>
         <v>-1.9764202067173997E-6</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8234574382123187E-6</v>
+      </c>
+      <c r="F62" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.8234574381677118E-6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>7.1000000000000056E-3</v>
       </c>
@@ -1462,8 +2032,16 @@
         <f t="shared" si="1"/>
         <v>-2.0098297717208169E-6</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8307461574558785E-6</v>
+      </c>
+      <c r="F63" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.8307461573532613E-6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>7.2000000000000059E-3</v>
       </c>
@@ -1478,8 +2056,16 @@
         <f t="shared" si="1"/>
         <v>-2.0432393301739182E-6</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8378324030000539E-6</v>
+      </c>
+      <c r="F64" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.8378324030193285E-6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>7.3000000000000061E-3</v>
       </c>
@@ -1494,8 +2080,16 @@
         <f t="shared" si="1"/>
         <v>-2.0766488945112016E-6</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8447245130290409E-6</v>
+      </c>
+      <c r="F65" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.8447245130290409E-6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>7.4000000000000064E-3</v>
       </c>
@@ -1510,8 +2104,16 @@
         <f t="shared" si="1"/>
         <v>-2.110058456294972E-6</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="1">
+        <f t="shared" si="2"/>
+        <v>-2.8514303462976699E-6</v>
+      </c>
+      <c r="F66" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.851430346344554E-6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>7.5000000000000067E-3</v>
       </c>
@@ -1519,15 +2121,23 @@
         <v>0.74999785653198137</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C90" si="2">A67*100</f>
+        <f t="shared" ref="C67:C90" si="4">A67*100</f>
         <v>0.75000000000000067</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D90" si="3">B67-C67</f>
+        <f t="shared" ref="D67:D90" si="5">B67-C67</f>
         <v>-2.1434680192999878E-6</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="1">
+        <f t="shared" ref="E67:E90" si="6">(B67/100-A67)/A67</f>
+        <v>-2.8579573590805257E-6</v>
+      </c>
+      <c r="F67" s="1">
+        <f t="shared" ref="F67:F90" si="7">(B67-C67)/C67</f>
+        <v>-2.8579573590666479E-6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>7.6000000000000069E-3</v>
       </c>
@@ -1535,15 +2145,23 @@
         <v>0.75999782312241981</v>
       </c>
       <c r="C68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.76000000000000068</v>
       </c>
       <c r="D68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.1768775808617136E-6</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.8643126064289443E-6</v>
+      </c>
+      <c r="F68" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.8643126063969891E-6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>7.7000000000000072E-3</v>
       </c>
@@ -1551,15 +2169,23 @@
         <v>0.76999778971285671</v>
       </c>
       <c r="C69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.77000000000000068</v>
       </c>
       <c r="D69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.2102871439777516E-6</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.870502784445263E-6</v>
+      </c>
+      <c r="F69" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.8705027843866877E-6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>7.8000000000000074E-3</v>
       </c>
@@ -1567,15 +2193,23 @@
         <v>0.77999775630329582</v>
       </c>
       <c r="C70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.78000000000000069</v>
       </c>
       <c r="D70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.2436967048733436E-6</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.8765342370571365E-6</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.8765342370171045E-6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>7.9000000000000077E-3</v>
       </c>
@@ -1583,15 +2217,23 @@
         <v>0.78999772289373338</v>
       </c>
       <c r="C71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.79000000000000081</v>
       </c>
       <c r="D71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.2771062674342701E-6</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.8824129967522379E-6</v>
+      </c>
+      <c r="F71" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.8824129967522375E-6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>8.0000000000000071E-3</v>
       </c>
@@ -1599,15 +2241,23 @@
         <v>0.7999976894841736</v>
       </c>
       <c r="C72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="D72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.3105158271086168E-6</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.8881447838770948E-6</v>
+      </c>
+      <c r="F72" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.8881447838857685E-6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>8.1000000000000065E-3</v>
       </c>
@@ -1615,15 +2265,23 @@
         <v>0.80999765607460938</v>
       </c>
       <c r="C73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.81000000000000061</v>
       </c>
       <c r="D73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.3439253912238556E-6</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.8937350509621788E-6</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.8937350508936467E-6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>8.2000000000000059E-3</v>
       </c>
@@ -1631,15 +2289,23 @@
         <v>0.8199976226650495</v>
       </c>
       <c r="C74">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.82000000000000062</v>
       </c>
       <c r="D74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.3773349511202468E-6</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.8991889647807868E-6</v>
+      </c>
+      <c r="F74" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.8991889647807868E-6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>8.3000000000000053E-3</v>
       </c>
@@ -1647,15 +2313,23 @@
         <v>0.82999758925548572</v>
       </c>
       <c r="C75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.83000000000000052</v>
       </c>
       <c r="D75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.4107445147913964E-6</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.90451146358737E-6</v>
+      </c>
+      <c r="F75" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9045114636040904E-6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>8.4000000000000047E-3</v>
       </c>
@@ -1663,15 +2337,23 @@
         <v>0.83999755584592495</v>
       </c>
       <c r="C76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.84000000000000052</v>
       </c>
       <c r="D76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.4441540755759661E-6</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9097072327211417E-6</v>
+      </c>
+      <c r="F76" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9097072328285293E-6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>8.5000000000000041E-3</v>
       </c>
@@ -1679,15 +2361,23 @@
         <v>0.84999752243636162</v>
       </c>
       <c r="C77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.85000000000000042</v>
       </c>
       <c r="D77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.4775636388030264E-6</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9147807515248074E-6</v>
+      </c>
+      <c r="F77" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9147807515329707E-6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>8.6000000000000035E-3</v>
       </c>
@@ -1695,15 +2385,23 @@
         <v>0.85999748902679851</v>
       </c>
       <c r="C78">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.86000000000000032</v>
       </c>
       <c r="D78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.5109732018080422E-6</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9197362811156615E-6</v>
+      </c>
+      <c r="F78" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9197362811721408E-6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>8.7000000000000029E-3</v>
       </c>
@@ -1711,15 +2409,23 @@
         <v>0.8699974556172374</v>
       </c>
       <c r="C79">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.87000000000000033</v>
       </c>
       <c r="D79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.5443827629256788E-6</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9245778882927077E-6</v>
+      </c>
+      <c r="F79" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9245778884203195E-6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>8.8000000000000023E-3</v>
       </c>
@@ -1727,15 +2433,23 @@
         <v>0.87999742220767585</v>
       </c>
       <c r="C80">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.88000000000000023</v>
       </c>
       <c r="D80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.5777923243763823E-6</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9293094595343856E-6</v>
+      </c>
+      <c r="F80" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9293094595186156E-6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>8.9000000000000017E-3</v>
       </c>
@@ -1743,15 +2457,23 @@
         <v>0.88999738879811241</v>
       </c>
       <c r="C81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.89000000000000012</v>
       </c>
       <c r="D81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.6112018877144649E-6</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.933934705281558E-6</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.933934705297151E-6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>9.0000000000000011E-3</v>
       </c>
@@ -1759,15 +2481,23 @@
         <v>0.89999735538854808</v>
       </c>
       <c r="C82">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.6446114520517483E-6</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9384571689463865E-6</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9384571689463865E-6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>9.1000000000000004E-3</v>
       </c>
@@ -1775,15 +2505,23 @@
         <v>0.90999732197898964</v>
       </c>
       <c r="C83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.91</v>
       </c>
       <c r="D83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.6780210103938273E-6</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9428802311333816E-6</v>
+      </c>
+      <c r="F83" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9428802312020078E-6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>9.1999999999999998E-3</v>
       </c>
@@ -1791,15 +2529,23 @@
         <v>0.91999728856942664</v>
       </c>
       <c r="C84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.91999999999999993</v>
       </c>
       <c r="D84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.7114305732878208E-6</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9472071448856085E-6</v>
+      </c>
+      <c r="F84" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9472071448780661E-6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>9.2999999999999992E-3</v>
       </c>
@@ -1807,15 +2553,23 @@
         <v>0.92999725515986564</v>
       </c>
       <c r="C85">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.92999999999999994</v>
       </c>
       <c r="D85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.7448401342944351E-6</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.951441004677362E-6</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9514410046176724E-6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>9.3999999999999986E-3</v>
       </c>
@@ -1823,15 +2577,23 @@
         <v>0.93999722175030298</v>
       </c>
       <c r="C86">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.93999999999999984</v>
       </c>
       <c r="D86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.7782496968553616E-6</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9555847840067919E-6</v>
+      </c>
+      <c r="F86" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9555847838886829E-6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>9.499999999999998E-3</v>
       </c>
@@ -1839,15 +2601,23 @@
         <v>0.9499971883407391</v>
       </c>
       <c r="C87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.94999999999999984</v>
       </c>
       <c r="D87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.8116592607485558E-6</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9596413269722699E-6</v>
+      </c>
+      <c r="F87" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9596413271037434E-6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>9.5999999999999974E-3</v>
       </c>
@@ -1855,15 +2625,23 @@
         <v>0.95999715493117843</v>
       </c>
       <c r="C88">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.95999999999999974</v>
       </c>
       <c r="D88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.8450688213110809E-6</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9636133555540609E-6</v>
+      </c>
+      <c r="F88" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9636133555323769E-6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>9.6999999999999968E-3</v>
       </c>
@@ -1871,15 +2649,23 @@
         <v>0.96999712152161544</v>
       </c>
       <c r="C89">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.96999999999999964</v>
       </c>
       <c r="D89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.8784783842050743E-6</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9675034889642072E-6</v>
+      </c>
+      <c r="F89" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9675034888712118E-6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>9.7999999999999962E-3</v>
       </c>
@@ -1887,12 +2673,20 @@
         <v>0.97999708811205211</v>
       </c>
       <c r="C90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.97999999999999965</v>
       </c>
       <c r="D90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-2.9118879475431569E-6</v>
+      </c>
+      <c r="E90" s="1">
+        <f t="shared" si="6"/>
+        <v>-2.9713142320736078E-6</v>
+      </c>
+      <c r="F90" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.9713142321868959E-6</v>
       </c>
     </row>
   </sheetData>

--- a/Homework2/my-simulation/question7.xlsx
+++ b/Homework2/my-simulation/question7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Document_forme\project_tiny\Cource_report\DTUD\Homework2\my-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE648C32-4901-4B8D-B4F7-325E999963D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715CAFEB-1113-495C-A439-04F19D32888A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2724B8F-81E9-4CBD-8F1B-A41AC1296333}"/>
   </bookViews>
@@ -509,15 +509,15 @@
         <v>0.1</v>
       </c>
       <c r="D2">
-        <f>B2-C2</f>
+        <f>ABS(B2-C2)</f>
         <v>2.8057829740135709E-8</v>
       </c>
       <c r="E2" s="1">
-        <f>(B2/100-A2)/A2</f>
+        <f>ABS(B2/100-A2)/A2</f>
         <v>2.80578297357989E-7</v>
       </c>
       <c r="F2" s="1">
-        <f>(B2-C2)/C2</f>
+        <f>ABS(B2-C2)/C2</f>
         <v>2.8057829740135709E-7</v>
       </c>
       <c r="G2" t="s">
@@ -525,7 +525,7 @@
       </c>
       <c r="H2" s="2">
         <f>MAX($E:$E)</f>
-        <v>2.80578297357989E-7</v>
+        <v>2.9713142320736078E-6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -540,23 +540,23 @@
         <v>0.11</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D66" si="1">B3-C3</f>
-        <v>-5.2560556323966168E-9</v>
+        <f t="shared" ref="D3:D66" si="1">ABS(B3-C3)</f>
+        <v>5.2560556323966168E-9</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E66" si="2">(B3/100-A3)/A3</f>
-        <v>-4.7782323986074078E-8</v>
+        <f t="shared" ref="E3:E66" si="2">ABS(B3/100-A3)/A3</f>
+        <v>4.7782323986074078E-8</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F66" si="3">(B3-C3)/C3</f>
-        <v>-4.7782323930878334E-8</v>
+        <f t="shared" ref="F3:F66" si="3">ABS(B3-C3)/C3</f>
+        <v>4.7782323930878334E-8</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="2">
         <f>MIN($E:$E)</f>
-        <v>-2.9713142320736078E-6</v>
+        <v>4.7782323986074078E-8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -572,15 +572,15 @@
       </c>
       <c r="D4">
         <f t="shared" si="1"/>
-        <v>-3.8665620941125134E-8</v>
+        <v>3.8665620941125134E-8</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" si="2"/>
-        <v>-3.2221350786439346E-7</v>
+        <v>3.2221350786439346E-7</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="3"/>
-        <v>-3.2221350784270941E-7</v>
+        <v>3.2221350784270941E-7</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -596,22 +596,22 @@
       </c>
       <c r="D5">
         <f t="shared" si="1"/>
-        <v>-7.2075181711817038E-8</v>
+        <v>7.2075181711817038E-8</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="2"/>
-        <v>-5.5442447474631691E-7</v>
+        <v>5.5442447474631691E-7</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="3"/>
-        <v>-5.5442447470628486E-7</v>
+        <v>5.5442447470628486E-7</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="2">
         <f>MAX($F:$F)</f>
-        <v>2.8057829740135709E-7</v>
+        <v>2.9713142321868959E-6</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -627,22 +627,22 @@
       </c>
       <c r="D6">
         <f t="shared" si="1"/>
-        <v>-1.054847435510986E-7</v>
+        <v>1.054847435510986E-7</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="2"/>
-        <v>-7.5346245394880938E-7</v>
+        <v>7.5346245394880938E-7</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="3"/>
-        <v>-7.5346245393641856E-7</v>
+        <v>7.5346245393641856E-7</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="2">
         <f>MIN($F:$F)</f>
-        <v>-2.9713142321868959E-6</v>
+        <v>4.7782323930878334E-8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -658,15 +658,15 @@
       </c>
       <c r="D7">
         <f t="shared" si="1"/>
-        <v>-1.3889430813818215E-7</v>
+        <v>1.3889430813818215E-7</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="2"/>
-        <v>-9.2596205428345958E-7</v>
+        <v>9.2596205428345958E-7</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="3"/>
-        <v>-9.2596205425454759E-7</v>
+        <v>9.2596205425454759E-7</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -682,22 +682,22 @@
       </c>
       <c r="D8">
         <f t="shared" si="1"/>
-        <v>-1.7230386695210598E-7</v>
+        <v>1.7230386695210598E-7</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="2"/>
-        <v>-1.076899168391031E-6</v>
+        <v>1.076899168391031E-6</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" si="3"/>
-        <v>-1.0768991684506621E-6</v>
+        <v>1.0768991684506621E-6</v>
       </c>
       <c r="G8" t="s">
         <v>4</v>
       </c>
       <c r="H8">
         <f>MAX(D2:D202)</f>
-        <v>2.8057829740135709E-8</v>
+        <v>2.9118879475431569E-6</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -713,22 +713,22 @@
       </c>
       <c r="D9">
         <f t="shared" si="1"/>
-        <v>-2.0571343065101111E-7</v>
+        <v>2.0571343065101111E-7</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="2"/>
-        <v>-1.2100790037835578E-6</v>
+        <v>1.2100790037835578E-6</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" si="3"/>
-        <v>-1.2100790038294767E-6</v>
+        <v>1.2100790038294767E-6</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
       </c>
       <c r="H9">
         <f>MIN(D2:D202)</f>
-        <v>-2.9118879475431569E-6</v>
+        <v>5.2560556323966168E-9</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -744,15 +744,15 @@
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>-2.391229914355808E-7</v>
+        <v>2.391229914355808E-7</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="2"/>
-        <v>-1.3284610634249932E-6</v>
+        <v>1.3284610634249932E-6</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="3"/>
-        <v>-1.3284610635310041E-6</v>
+        <v>1.3284610635310041E-6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -768,15 +768,15 @@
       </c>
       <c r="D11">
         <f t="shared" si="1"/>
-        <v>-2.7253255333037352E-7</v>
+        <v>2.7253255333037352E-7</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="2"/>
-        <v>-1.4343818596791952E-6</v>
+        <v>1.4343818596791952E-6</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" si="3"/>
-        <v>-1.4343818596335446E-6</v>
+        <v>1.4343818596335446E-6</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -799,15 +799,15 @@
       </c>
       <c r="D12">
         <f t="shared" si="1"/>
-        <v>-3.0594211600232235E-7</v>
+        <v>3.0594211600232235E-7</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="2"/>
-        <v>-1.5297105799942641E-6</v>
+        <v>1.5297105799942641E-6</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" si="3"/>
-        <v>-1.5297105800116115E-6</v>
+        <v>1.5297105800116115E-6</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -830,15 +830,15 @@
       </c>
       <c r="D13">
         <f t="shared" si="1"/>
-        <v>-3.3935167687015877E-7</v>
+        <v>3.3935167687015877E-7</v>
       </c>
       <c r="E13" s="1">
-        <f>(B13/100-A13)/A13</f>
-        <v>-1.6159603660979385E-6</v>
+        <f t="shared" si="2"/>
+        <v>1.6159603660979385E-6</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" si="3"/>
-        <v>-1.615960366048375E-6</v>
+        <v>1.615960366048375E-6</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -854,15 +854,15 @@
       </c>
       <c r="D14">
         <f t="shared" si="1"/>
-        <v>-3.7276123679430562E-7</v>
+        <v>3.7276123679430562E-7</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="2"/>
-        <v>-1.6943692582190153E-6</v>
+        <v>1.6943692582190153E-6</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="3"/>
-        <v>-1.6943692581559346E-6</v>
+        <v>1.6943692581559346E-6</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -878,15 +878,15 @@
       </c>
       <c r="D15">
         <f t="shared" si="1"/>
-        <v>-4.0617079946625445E-7</v>
+        <v>4.0617079946625445E-7</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="2"/>
-        <v>-1.7659599976869096E-6</v>
+        <v>1.7659599976869096E-6</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="3"/>
-        <v>-1.7659599976793674E-6</v>
+        <v>1.7659599976793674E-6</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -902,15 +902,15 @@
       </c>
       <c r="D16">
         <f t="shared" si="1"/>
-        <v>-4.3958036133329159E-7</v>
+        <v>4.3958036133329159E-7</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="2"/>
-        <v>-1.8315848387658389E-6</v>
+        <v>1.8315848387658389E-6</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="3"/>
-        <v>-1.831584838888715E-6</v>
+        <v>1.831584838888715E-6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -926,15 +926,15 @@
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>-4.729899251709746E-7</v>
+        <v>4.729899251709746E-7</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="2"/>
-        <v>-1.8919597007116542E-6</v>
+        <v>1.8919597007116542E-6</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="3"/>
-        <v>-1.8919597006838986E-6</v>
+        <v>1.8919597006838986E-6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -950,15 +950,15 @@
       </c>
       <c r="D18">
         <f t="shared" si="1"/>
-        <v>-5.0639948501185472E-7</v>
+        <v>5.0639948501185472E-7</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="2"/>
-        <v>-1.9476903269953605E-6</v>
+        <v>1.9476903269953605E-6</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="3"/>
-        <v>-1.9476903269686722E-6</v>
+        <v>1.9476903269686722E-6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -974,15 +974,15 @@
       </c>
       <c r="D19">
         <f t="shared" si="1"/>
-        <v>-5.3980904690664744E-7</v>
+        <v>5.3980904690664744E-7</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="2"/>
-        <v>-1.9992927664494148E-6</v>
+        <v>1.9992927664494148E-6</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" si="3"/>
-        <v>-1.9992927663209169E-6</v>
+        <v>1.9992927663209169E-6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -998,15 +998,15 @@
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>-5.7321860996717433E-7</v>
+        <v>5.7321860996717433E-7</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="2"/>
-        <v>-2.0472093212431877E-6</v>
+        <v>2.0472093212431877E-6</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" si="3"/>
-        <v>-2.0472093213113374E-6</v>
+        <v>2.0472093213113374E-6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1022,15 +1022,15 @@
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>-6.0662817080725517E-7</v>
+        <v>6.0662817080725517E-7</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="2"/>
-        <v>-2.0918212787234719E-6</v>
+        <v>2.0918212787234719E-6</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" si="3"/>
-        <v>-2.0918212786457084E-6</v>
+        <v>2.0918212786457084E-6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1046,15 +1046,15 @@
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>-6.4003773059262414E-7</v>
+        <v>6.4003773059262414E-7</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" si="2"/>
-        <v>-2.1334591019465027E-6</v>
+        <v>2.1334591019465027E-6</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" si="3"/>
-        <v>-2.1334591019754145E-6</v>
+        <v>2.1334591019754145E-6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1070,15 +1070,15 @@
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>-6.7344729265395031E-7</v>
+        <v>6.7344729265395031E-7</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="2"/>
-        <v>-2.1724106215482951E-6</v>
+        <v>2.1724106215482951E-6</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" si="3"/>
-        <v>-2.1724106214643571E-6</v>
+        <v>2.1724106214643571E-6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1094,15 +1094,15 @@
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>-7.0685685543692145E-7</v>
+        <v>7.0685685543692145E-7</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" si="2"/>
-        <v>-2.2089276732078547E-6</v>
+        <v>2.2089276732078547E-6</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" si="3"/>
-        <v>-2.2089276732403808E-6</v>
+        <v>2.2089276732403808E-6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1118,15 +1118,15 @@
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>-7.4026641722069186E-7</v>
+        <v>7.4026641722069186E-7</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" si="2"/>
-        <v>-2.2432315671987561E-6</v>
+        <v>2.2432315671987561E-6</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" si="3"/>
-        <v>-2.2432315673354308E-6</v>
+        <v>2.2432315673354308E-6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1142,15 +1142,15 @@
       </c>
       <c r="D26">
         <f t="shared" si="1"/>
-        <v>-7.736759802257076E-7</v>
+        <v>7.736759802257076E-7</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="2"/>
-        <v>-2.2755175888991415E-6</v>
+        <v>2.2755175888991415E-6</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" si="3"/>
-        <v>-2.2755175888991415E-6</v>
+        <v>2.2755175888991415E-6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1166,15 +1166,15 @@
       </c>
       <c r="D27">
         <f t="shared" si="1"/>
-        <v>-8.0708554128783305E-7</v>
+        <v>8.0708554128783305E-7</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" si="2"/>
-        <v>-2.3059586893739845E-6</v>
+        <v>2.3059586893739845E-6</v>
       </c>
       <c r="F27" s="1">
         <f t="shared" si="3"/>
-        <v>-2.3059586893938102E-6</v>
+        <v>2.3059586893938102E-6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1190,15 +1190,15 @@
       </c>
       <c r="D28">
         <f t="shared" si="1"/>
-        <v>-8.4049510323813692E-7</v>
+        <v>8.4049510323813692E-7</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="2"/>
-        <v>-2.3347086201300308E-6</v>
+        <v>2.3347086201300308E-6</v>
       </c>
       <c r="F28" s="1">
         <f t="shared" si="3"/>
-        <v>-2.3347086201059373E-6</v>
+        <v>2.3347086201059373E-6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1214,15 +1214,15 @@
       </c>
       <c r="D29">
         <f t="shared" si="1"/>
-        <v>-8.7390466418924007E-7</v>
+        <v>8.7390466418924007E-7</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="2"/>
-        <v>-2.3619044977618743E-6</v>
+        <v>2.3619044977618743E-6</v>
       </c>
       <c r="F29" s="1">
         <f t="shared" si="3"/>
-        <v>-2.3619044978087584E-6</v>
+        <v>2.3619044978087584E-6</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1238,15 +1238,15 @@
       </c>
       <c r="D30">
         <f t="shared" si="1"/>
-        <v>-9.073142270832335E-7</v>
+        <v>9.073142270832335E-7</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="2"/>
-        <v>-2.3876690186629152E-6</v>
+        <v>2.3876690186629152E-6</v>
       </c>
       <c r="F30" s="1">
         <f t="shared" si="3"/>
-        <v>-2.3876690186400898E-6</v>
+        <v>2.3876690186400898E-6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1262,15 +1262,15 @@
       </c>
       <c r="D31">
         <f t="shared" si="1"/>
-        <v>-9.4072378892251507E-7</v>
+        <v>9.4072378892251507E-7</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" si="2"/>
-        <v>-2.412112279301846E-6</v>
+        <v>2.412112279301846E-6</v>
       </c>
       <c r="F31" s="1">
         <f t="shared" si="3"/>
-        <v>-2.4121122792885019E-6</v>
+        <v>2.4121122792885019E-6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1286,15 +1286,15 @@
       </c>
       <c r="D32">
         <f t="shared" si="1"/>
-        <v>-9.7413335092833009E-7</v>
+        <v>9.7413335092833009E-7</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="2"/>
-        <v>-2.4353333772340907E-6</v>
+        <v>2.4353333772340907E-6</v>
       </c>
       <c r="F32" s="1">
         <f t="shared" si="3"/>
-        <v>-2.4353333773208269E-6</v>
+        <v>2.4353333773208269E-6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1310,15 +1310,15 @@
       </c>
       <c r="D33">
         <f t="shared" si="1"/>
-        <v>-1.0075429111022771E-6</v>
+        <v>1.0075429111022771E-6</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="2"/>
-        <v>-2.4574217343450268E-6</v>
+        <v>2.4574217343450268E-6</v>
       </c>
       <c r="F33" s="1">
         <f t="shared" si="3"/>
-        <v>-2.4574217343957993E-6</v>
+        <v>2.4574217343957993E-6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1334,15 +1334,15 @@
       </c>
       <c r="D34">
         <f t="shared" si="1"/>
-        <v>-1.0409524741072929E-6</v>
+        <v>1.0409524741072929E-6</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="2"/>
-        <v>-2.478458271741856E-6</v>
+        <v>2.478458271741856E-6</v>
       </c>
       <c r="F34" s="1">
         <f t="shared" si="3"/>
-        <v>-2.4784582716840316E-6</v>
+        <v>2.4784582716840316E-6</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1358,15 +1358,15 @@
       </c>
       <c r="D35">
         <f t="shared" si="1"/>
-        <v>-1.0743620349473737E-6</v>
+        <v>1.0743620349473737E-6</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" si="2"/>
-        <v>-2.4985163602943197E-6</v>
+        <v>2.4985163602943197E-6</v>
       </c>
       <c r="F35" s="1">
         <f t="shared" si="3"/>
-        <v>-2.4985163603427306E-6</v>
+        <v>2.4985163603427306E-6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1382,15 +1382,15 @@
       </c>
       <c r="D36">
         <f t="shared" si="1"/>
-        <v>-1.107771598896079E-6</v>
+        <v>1.107771598896079E-6</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" si="2"/>
-        <v>-2.5176627248426677E-6</v>
+        <v>2.5176627248426677E-6</v>
       </c>
       <c r="F36" s="1">
         <f t="shared" si="3"/>
-        <v>-2.517662724763817E-6</v>
+        <v>2.517662724763817E-6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1406,15 +1406,15 @@
       </c>
       <c r="D37">
         <f t="shared" si="1"/>
-        <v>-1.1411811591810483E-6</v>
+        <v>1.1411811591810483E-6</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="2"/>
-        <v>-2.5359581313746636E-6</v>
+        <v>2.5359581313746636E-6</v>
       </c>
       <c r="F37" s="1">
         <f t="shared" si="3"/>
-        <v>-2.5359581315134415E-6</v>
+        <v>2.5359581315134415E-6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1430,15 +1430,15 @@
       </c>
       <c r="D38">
         <f t="shared" si="1"/>
-        <v>-1.1745907231852648E-6</v>
+        <v>1.1745907231852648E-6</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="2"/>
-        <v>-2.5534580939338069E-6</v>
+        <v>2.5534580939338069E-6</v>
       </c>
       <c r="F38" s="1">
         <f t="shared" si="3"/>
-        <v>-2.5534580938810109E-6</v>
+        <v>2.5534580938810109E-6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1454,15 +1454,15 @@
       </c>
       <c r="D39">
         <f t="shared" si="1"/>
-        <v>-1.2080002814163215E-6</v>
+        <v>1.2080002814163215E-6</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="2"/>
-        <v>-2.5702133646860511E-6</v>
+        <v>2.5702133646860511E-6</v>
       </c>
       <c r="F39" s="1">
         <f t="shared" si="3"/>
-        <v>-2.5702133647155783E-6</v>
+        <v>2.5702133647155783E-6</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,15 +1478,15 @@
       </c>
       <c r="D40">
         <f t="shared" si="1"/>
-        <v>-1.2414098443658261E-6</v>
+        <v>1.2414098443658261E-6</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="2"/>
-        <v>-2.5862705090954714E-6</v>
+        <v>2.5862705090954714E-6</v>
       </c>
       <c r="F40" s="1">
         <f t="shared" si="3"/>
-        <v>-2.5862705090954714E-6</v>
+        <v>2.5862705090954714E-6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1502,15 +1502,15 @@
       </c>
       <c r="D41">
         <f t="shared" si="1"/>
-        <v>-1.2748194064826635E-6</v>
+        <v>1.2748194064826635E-6</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="2"/>
-        <v>-2.6016722580854016E-6</v>
+        <v>2.6016722580854016E-6</v>
       </c>
       <c r="F41" s="1">
         <f t="shared" si="3"/>
-        <v>-2.6016722581278846E-6</v>
+        <v>2.6016722581278846E-6</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1526,15 +1526,15 @@
       </c>
       <c r="D42">
         <f t="shared" si="1"/>
-        <v>-1.3082289705979022E-6</v>
+        <v>1.3082289705979022E-6</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="2"/>
-        <v>-2.6164579412790712E-6</v>
+        <v>2.6164579412790712E-6</v>
       </c>
       <c r="F42" s="1">
         <f t="shared" si="3"/>
-        <v>-2.6164579411958044E-6</v>
+        <v>2.6164579411958044E-6</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1550,15 +1550,15 @@
       </c>
       <c r="D43">
         <f t="shared" si="1"/>
-        <v>-1.3416385316045165E-6</v>
+        <v>1.3416385316045165E-6</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" si="2"/>
-        <v>-2.630663787466639E-6</v>
+        <v>2.630663787466639E-6</v>
       </c>
       <c r="F43" s="1">
         <f t="shared" si="3"/>
-        <v>-2.6306637874598361E-6</v>
+        <v>2.6306637874598361E-6</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1574,15 +1574,15 @@
       </c>
       <c r="D44">
         <f t="shared" si="1"/>
-        <v>-1.3750480925001085E-6</v>
+        <v>1.3750480925001085E-6</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="2"/>
-        <v>-2.644323254954685E-6</v>
+        <v>2.644323254954685E-6</v>
       </c>
       <c r="F44" s="1">
         <f t="shared" si="3"/>
-        <v>-2.644323254807901E-6</v>
+        <v>2.644323254807901E-6</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1598,15 +1598,15 @@
       </c>
       <c r="D45">
         <f t="shared" si="1"/>
-        <v>-1.4084576541728566E-6</v>
+        <v>1.4084576541728566E-6</v>
       </c>
       <c r="E45" s="1">
         <f t="shared" si="2"/>
-        <v>-2.6574672719849807E-6</v>
+        <v>2.6574672719849807E-6</v>
       </c>
       <c r="F45" s="1">
         <f t="shared" si="3"/>
-        <v>-2.6574672720242572E-6</v>
+        <v>2.6574672720242572E-6</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1622,15 +1622,15 @@
       </c>
       <c r="D46">
         <f t="shared" si="1"/>
-        <v>-1.4418672179550285E-6</v>
+        <v>1.4418672179550285E-6</v>
       </c>
       <c r="E46" s="1">
         <f t="shared" si="2"/>
-        <v>-2.6701244775852733E-6</v>
+        <v>2.6701244775852733E-6</v>
       </c>
       <c r="F46" s="1">
         <f t="shared" si="3"/>
-        <v>-2.6701244776944965E-6</v>
+        <v>2.6701244776944965E-6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1646,15 +1646,15 @@
       </c>
       <c r="D47">
         <f t="shared" si="1"/>
-        <v>-1.4752767779624421E-6</v>
+        <v>1.4752767779624421E-6</v>
       </c>
       <c r="E47" s="1">
         <f t="shared" si="2"/>
-        <v>-2.6823214143825456E-6</v>
+        <v>2.6823214143825456E-6</v>
       </c>
       <c r="F47" s="1">
         <f t="shared" si="3"/>
-        <v>-2.6823214144771668E-6</v>
+        <v>2.6823214144771668E-6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1670,15 +1670,15 @@
       </c>
       <c r="D48">
         <f t="shared" si="1"/>
-        <v>-1.5086863415225693E-6</v>
+        <v>1.5086863415225693E-6</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" si="2"/>
-        <v>-2.6940827527994139E-6</v>
+        <v>2.6940827527994139E-6</v>
       </c>
       <c r="F48" s="1">
         <f t="shared" si="3"/>
-        <v>-2.6940827527188729E-6</v>
+        <v>2.6940827527188729E-6</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1694,15 +1694,15 @@
       </c>
       <c r="D49">
         <f t="shared" si="1"/>
-        <v>-1.5420959037504289E-6</v>
+        <v>1.5420959037504289E-6</v>
       </c>
       <c r="E49" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7054314100884711E-6</v>
+        <v>2.7054314100884711E-6</v>
       </c>
       <c r="F49" s="1">
         <f t="shared" si="3"/>
-        <v>-2.7054314100884711E-6</v>
+        <v>2.7054314100884711E-6</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1718,15 +1718,15 @@
       </c>
       <c r="D50">
         <f t="shared" si="1"/>
-        <v>-1.5755054637578425E-6</v>
+        <v>1.5755054637578425E-6</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7163887306289325E-6</v>
+        <v>2.7163887306289325E-6</v>
       </c>
       <c r="F50" s="1">
         <f t="shared" si="3"/>
-        <v>-2.716388730616969E-6</v>
+        <v>2.716388730616969E-6</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1742,15 +1742,15 @@
       </c>
       <c r="D51">
         <f t="shared" si="1"/>
-        <v>-1.6089150260967244E-6</v>
+        <v>1.6089150260967244E-6</v>
       </c>
       <c r="E51" s="1">
         <f t="shared" si="2"/>
-        <v>-2.726974620397074E-6</v>
+        <v>2.726974620397074E-6</v>
       </c>
       <c r="F51" s="1">
         <f t="shared" si="3"/>
-        <v>-2.7269746205029213E-6</v>
+        <v>2.7269746205029213E-6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,15 +1766,15 @@
       </c>
       <c r="D52">
         <f t="shared" si="1"/>
-        <v>-1.6423245869923164E-6</v>
+        <v>1.6423245869923164E-6</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7372076448599799E-6</v>
+        <v>2.7372076448599799E-6</v>
       </c>
       <c r="F52" s="1">
         <f t="shared" si="3"/>
-        <v>-2.7372076449871928E-6</v>
+        <v>2.7372076449871928E-6</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1790,15 +1790,15 @@
       </c>
       <c r="D53">
         <f t="shared" si="1"/>
-        <v>-1.6757341494422207E-6</v>
+        <v>1.6757341494422207E-6</v>
       </c>
       <c r="E53" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7471051630257203E-6</v>
+        <v>2.7471051630257203E-6</v>
       </c>
       <c r="F53" s="1">
         <f t="shared" si="3"/>
-        <v>-2.7471051630200325E-6</v>
+        <v>2.7471051630200325E-6</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1814,15 +1814,15 @@
       </c>
       <c r="D54">
         <f t="shared" si="1"/>
-        <v>-1.7091437105598573E-6</v>
+        <v>1.7091437105598573E-6</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7566834041735678E-6</v>
+        <v>2.7566834041735678E-6</v>
       </c>
       <c r="F54" s="1">
         <f t="shared" si="3"/>
-        <v>-2.7566834041288004E-6</v>
+        <v>2.7566834041288004E-6</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1838,15 +1838,15 @@
       </c>
       <c r="D55">
         <f t="shared" si="1"/>
-        <v>-1.7425532765624752E-6</v>
+        <v>1.7425532765624752E-6</v>
       </c>
       <c r="E55" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7659575818837464E-6</v>
+        <v>2.7659575818837464E-6</v>
       </c>
       <c r="F55" s="1">
         <f t="shared" si="3"/>
-        <v>-2.765957581845197E-6</v>
+        <v>2.765957581845197E-6</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1862,15 +1862,15 @@
       </c>
       <c r="D56">
         <f t="shared" si="1"/>
-        <v>-1.7759628379021564E-6</v>
+        <v>1.7759628379021564E-6</v>
       </c>
       <c r="E56" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7749419342221176E-6</v>
+        <v>2.7749419342221176E-6</v>
       </c>
       <c r="F56" s="1">
         <f t="shared" si="3"/>
-        <v>-2.7749419342221176E-6</v>
+        <v>2.7749419342221176E-6</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,15 +1886,15 @@
       </c>
       <c r="D57">
         <f t="shared" si="1"/>
-        <v>-1.8093723982426368E-6</v>
+        <v>1.8093723982426368E-6</v>
       </c>
       <c r="E57" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7836498434822345E-6</v>
+        <v>2.7836498434822345E-6</v>
       </c>
       <c r="F57" s="1">
         <f t="shared" si="3"/>
-        <v>-2.783649843450209E-6</v>
+        <v>2.783649843450209E-6</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1910,15 +1910,15 @@
       </c>
       <c r="D58">
         <f t="shared" si="1"/>
-        <v>-1.8427819603594742E-6</v>
+        <v>1.8427819603594742E-6</v>
       </c>
       <c r="E58" s="1">
         <f t="shared" si="2"/>
-        <v>-2.7920938792011164E-6</v>
+        <v>2.7920938792011164E-6</v>
       </c>
       <c r="F58" s="1">
         <f t="shared" si="3"/>
-        <v>-2.7920938793325348E-6</v>
+        <v>2.7920938793325348E-6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1934,15 +1934,15 @@
       </c>
       <c r="D59">
         <f t="shared" si="1"/>
-        <v>-1.8761915228093784E-6</v>
+        <v>1.8761915228093784E-6</v>
       </c>
       <c r="E59" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8002858549290124E-6</v>
+        <v>2.8002858549290124E-6</v>
       </c>
       <c r="F59" s="1">
         <f t="shared" si="3"/>
-        <v>-2.8002858549393687E-6</v>
+        <v>2.8002858549393687E-6</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1958,15 +1958,15 @@
       </c>
       <c r="D60">
         <f t="shared" si="1"/>
-        <v>-1.9096010842600819E-6</v>
+        <v>1.9096010842600819E-6</v>
       </c>
       <c r="E60" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8082368886636847E-6</v>
+        <v>2.8082368886636847E-6</v>
       </c>
       <c r="F60" s="1">
         <f t="shared" si="3"/>
-        <v>-2.8082368886177653E-6</v>
+        <v>2.8082368886177653E-6</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1982,15 +1982,15 @@
       </c>
       <c r="D61">
         <f t="shared" si="1"/>
-        <v>-1.9430106478202092E-6</v>
+        <v>1.9430106478202092E-6</v>
       </c>
       <c r="E61" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8159574606693348E-6</v>
+        <v>2.8159574606693348E-6</v>
       </c>
       <c r="F61" s="1">
         <f t="shared" si="3"/>
-        <v>-2.8159574606089969E-6</v>
+        <v>2.8159574606089969E-6</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2006,15 +2006,15 @@
       </c>
       <c r="D62">
         <f t="shared" si="1"/>
-        <v>-1.9764202067173997E-6</v>
+        <v>1.9764202067173997E-6</v>
       </c>
       <c r="E62" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8234574382123187E-6</v>
+        <v>2.8234574382123187E-6</v>
       </c>
       <c r="F62" s="1">
         <f t="shared" si="3"/>
-        <v>-2.8234574381677118E-6</v>
+        <v>2.8234574381677118E-6</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2030,15 +2030,15 @@
       </c>
       <c r="D63">
         <f t="shared" si="1"/>
-        <v>-2.0098297717208169E-6</v>
+        <v>2.0098297717208169E-6</v>
       </c>
       <c r="E63" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8307461574558785E-6</v>
+        <v>2.8307461574558785E-6</v>
       </c>
       <c r="F63" s="1">
         <f t="shared" si="3"/>
-        <v>-2.8307461573532613E-6</v>
+        <v>2.8307461573532613E-6</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2054,15 +2054,15 @@
       </c>
       <c r="D64">
         <f t="shared" si="1"/>
-        <v>-2.0432393301739182E-6</v>
+        <v>2.0432393301739182E-6</v>
       </c>
       <c r="E64" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8378324030000539E-6</v>
+        <v>2.8378324030000539E-6</v>
       </c>
       <c r="F64" s="1">
         <f t="shared" si="3"/>
-        <v>-2.8378324030193285E-6</v>
+        <v>2.8378324030193285E-6</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2078,15 +2078,15 @@
       </c>
       <c r="D65">
         <f t="shared" si="1"/>
-        <v>-2.0766488945112016E-6</v>
+        <v>2.0766488945112016E-6</v>
       </c>
       <c r="E65" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8447245130290409E-6</v>
+        <v>2.8447245130290409E-6</v>
       </c>
       <c r="F65" s="1">
         <f t="shared" si="3"/>
-        <v>-2.8447245130290409E-6</v>
+        <v>2.8447245130290409E-6</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2102,15 +2102,15 @@
       </c>
       <c r="D66">
         <f t="shared" si="1"/>
-        <v>-2.110058456294972E-6</v>
+        <v>2.110058456294972E-6</v>
       </c>
       <c r="E66" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8514303462976699E-6</v>
+        <v>2.8514303462976699E-6</v>
       </c>
       <c r="F66" s="1">
         <f t="shared" si="3"/>
-        <v>-2.851430346344554E-6</v>
+        <v>2.851430346344554E-6</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2125,16 +2125,16 @@
         <v>0.75000000000000067</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D90" si="5">B67-C67</f>
-        <v>-2.1434680192999878E-6</v>
+        <f t="shared" ref="D67:D90" si="5">ABS(B67-C67)</f>
+        <v>2.1434680192999878E-6</v>
       </c>
       <c r="E67" s="1">
-        <f t="shared" ref="E67:E90" si="6">(B67/100-A67)/A67</f>
-        <v>-2.8579573590805257E-6</v>
+        <f t="shared" ref="E67:E90" si="6">ABS(B67/100-A67)/A67</f>
+        <v>2.8579573590805257E-6</v>
       </c>
       <c r="F67" s="1">
-        <f t="shared" ref="F67:F90" si="7">(B67-C67)/C67</f>
-        <v>-2.8579573590666479E-6</v>
+        <f t="shared" ref="F67:F90" si="7">ABS(B67-C67)/C67</f>
+        <v>2.8579573590666479E-6</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2150,15 +2150,15 @@
       </c>
       <c r="D68">
         <f t="shared" si="5"/>
-        <v>-2.1768775808617136E-6</v>
+        <v>2.1768775808617136E-6</v>
       </c>
       <c r="E68" s="1">
         <f t="shared" si="6"/>
-        <v>-2.8643126064289443E-6</v>
+        <v>2.8643126064289443E-6</v>
       </c>
       <c r="F68" s="1">
         <f t="shared" si="7"/>
-        <v>-2.8643126063969891E-6</v>
+        <v>2.8643126063969891E-6</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2174,15 +2174,15 @@
       </c>
       <c r="D69">
         <f t="shared" si="5"/>
-        <v>-2.2102871439777516E-6</v>
+        <v>2.2102871439777516E-6</v>
       </c>
       <c r="E69" s="1">
         <f t="shared" si="6"/>
-        <v>-2.870502784445263E-6</v>
+        <v>2.870502784445263E-6</v>
       </c>
       <c r="F69" s="1">
         <f t="shared" si="7"/>
-        <v>-2.8705027843866877E-6</v>
+        <v>2.8705027843866877E-6</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2198,15 +2198,15 @@
       </c>
       <c r="D70">
         <f t="shared" si="5"/>
-        <v>-2.2436967048733436E-6</v>
+        <v>2.2436967048733436E-6</v>
       </c>
       <c r="E70" s="1">
         <f t="shared" si="6"/>
-        <v>-2.8765342370571365E-6</v>
+        <v>2.8765342370571365E-6</v>
       </c>
       <c r="F70" s="1">
         <f t="shared" si="7"/>
-        <v>-2.8765342370171045E-6</v>
+        <v>2.8765342370171045E-6</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2222,15 +2222,15 @@
       </c>
       <c r="D71">
         <f t="shared" si="5"/>
-        <v>-2.2771062674342701E-6</v>
+        <v>2.2771062674342701E-6</v>
       </c>
       <c r="E71" s="1">
         <f t="shared" si="6"/>
-        <v>-2.8824129967522379E-6</v>
+        <v>2.8824129967522379E-6</v>
       </c>
       <c r="F71" s="1">
         <f t="shared" si="7"/>
-        <v>-2.8824129967522375E-6</v>
+        <v>2.8824129967522375E-6</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2246,15 +2246,15 @@
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>-2.3105158271086168E-6</v>
+        <v>2.3105158271086168E-6</v>
       </c>
       <c r="E72" s="1">
         <f t="shared" si="6"/>
-        <v>-2.8881447838770948E-6</v>
+        <v>2.8881447838770948E-6</v>
       </c>
       <c r="F72" s="1">
         <f t="shared" si="7"/>
-        <v>-2.8881447838857685E-6</v>
+        <v>2.8881447838857685E-6</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2270,15 +2270,15 @@
       </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>-2.3439253912238556E-6</v>
+        <v>2.3439253912238556E-6</v>
       </c>
       <c r="E73" s="1">
         <f t="shared" si="6"/>
-        <v>-2.8937350509621788E-6</v>
+        <v>2.8937350509621788E-6</v>
       </c>
       <c r="F73" s="1">
         <f t="shared" si="7"/>
-        <v>-2.8937350508936467E-6</v>
+        <v>2.8937350508936467E-6</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2294,15 +2294,15 @@
       </c>
       <c r="D74">
         <f t="shared" si="5"/>
-        <v>-2.3773349511202468E-6</v>
+        <v>2.3773349511202468E-6</v>
       </c>
       <c r="E74" s="1">
         <f t="shared" si="6"/>
-        <v>-2.8991889647807868E-6</v>
+        <v>2.8991889647807868E-6</v>
       </c>
       <c r="F74" s="1">
         <f t="shared" si="7"/>
-        <v>-2.8991889647807868E-6</v>
+        <v>2.8991889647807868E-6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2318,15 +2318,15 @@
       </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>-2.4107445147913964E-6</v>
+        <v>2.4107445147913964E-6</v>
       </c>
       <c r="E75" s="1">
         <f t="shared" si="6"/>
-        <v>-2.90451146358737E-6</v>
+        <v>2.90451146358737E-6</v>
       </c>
       <c r="F75" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9045114636040904E-6</v>
+        <v>2.9045114636040904E-6</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2342,15 +2342,15 @@
       </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>-2.4441540755759661E-6</v>
+        <v>2.4441540755759661E-6</v>
       </c>
       <c r="E76" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9097072327211417E-6</v>
+        <v>2.9097072327211417E-6</v>
       </c>
       <c r="F76" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9097072328285293E-6</v>
+        <v>2.9097072328285293E-6</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2366,15 +2366,15 @@
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>-2.4775636388030264E-6</v>
+        <v>2.4775636388030264E-6</v>
       </c>
       <c r="E77" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9147807515248074E-6</v>
+        <v>2.9147807515248074E-6</v>
       </c>
       <c r="F77" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9147807515329707E-6</v>
+        <v>2.9147807515329707E-6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2390,15 +2390,15 @@
       </c>
       <c r="D78">
         <f t="shared" si="5"/>
-        <v>-2.5109732018080422E-6</v>
+        <v>2.5109732018080422E-6</v>
       </c>
       <c r="E78" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9197362811156615E-6</v>
+        <v>2.9197362811156615E-6</v>
       </c>
       <c r="F78" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9197362811721408E-6</v>
+        <v>2.9197362811721408E-6</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2414,15 +2414,15 @@
       </c>
       <c r="D79">
         <f t="shared" si="5"/>
-        <v>-2.5443827629256788E-6</v>
+        <v>2.5443827629256788E-6</v>
       </c>
       <c r="E79" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9245778882927077E-6</v>
+        <v>2.9245778882927077E-6</v>
       </c>
       <c r="F79" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9245778884203195E-6</v>
+        <v>2.9245778884203195E-6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="D80">
         <f t="shared" si="5"/>
-        <v>-2.5777923243763823E-6</v>
+        <v>2.5777923243763823E-6</v>
       </c>
       <c r="E80" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9293094595343856E-6</v>
+        <v>2.9293094595343856E-6</v>
       </c>
       <c r="F80" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9293094595186156E-6</v>
+        <v>2.9293094595186156E-6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2462,15 +2462,15 @@
       </c>
       <c r="D81">
         <f t="shared" si="5"/>
-        <v>-2.6112018877144649E-6</v>
+        <v>2.6112018877144649E-6</v>
       </c>
       <c r="E81" s="1">
         <f t="shared" si="6"/>
-        <v>-2.933934705281558E-6</v>
+        <v>2.933934705281558E-6</v>
       </c>
       <c r="F81" s="1">
         <f t="shared" si="7"/>
-        <v>-2.933934705297151E-6</v>
+        <v>2.933934705297151E-6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,15 +2486,15 @@
       </c>
       <c r="D82">
         <f t="shared" si="5"/>
-        <v>-2.6446114520517483E-6</v>
+        <v>2.6446114520517483E-6</v>
       </c>
       <c r="E82" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9384571689463865E-6</v>
+        <v>2.9384571689463865E-6</v>
       </c>
       <c r="F82" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9384571689463865E-6</v>
+        <v>2.9384571689463865E-6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,15 +2510,15 @@
       </c>
       <c r="D83">
         <f t="shared" si="5"/>
-        <v>-2.6780210103938273E-6</v>
+        <v>2.6780210103938273E-6</v>
       </c>
       <c r="E83" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9428802311333816E-6</v>
+        <v>2.9428802311333816E-6</v>
       </c>
       <c r="F83" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9428802312020078E-6</v>
+        <v>2.9428802312020078E-6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2534,15 +2534,15 @@
       </c>
       <c r="D84">
         <f t="shared" si="5"/>
-        <v>-2.7114305732878208E-6</v>
+        <v>2.7114305732878208E-6</v>
       </c>
       <c r="E84" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9472071448856085E-6</v>
+        <v>2.9472071448856085E-6</v>
       </c>
       <c r="F84" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9472071448780661E-6</v>
+        <v>2.9472071448780661E-6</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,15 +2558,15 @@
       </c>
       <c r="D85">
         <f t="shared" si="5"/>
-        <v>-2.7448401342944351E-6</v>
+        <v>2.7448401342944351E-6</v>
       </c>
       <c r="E85" s="1">
         <f t="shared" si="6"/>
-        <v>-2.951441004677362E-6</v>
+        <v>2.951441004677362E-6</v>
       </c>
       <c r="F85" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9514410046176724E-6</v>
+        <v>2.9514410046176724E-6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2582,15 +2582,15 @@
       </c>
       <c r="D86">
         <f t="shared" si="5"/>
-        <v>-2.7782496968553616E-6</v>
+        <v>2.7782496968553616E-6</v>
       </c>
       <c r="E86" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9555847840067919E-6</v>
+        <v>2.9555847840067919E-6</v>
       </c>
       <c r="F86" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9555847838886829E-6</v>
+        <v>2.9555847838886829E-6</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2606,15 +2606,15 @@
       </c>
       <c r="D87">
         <f t="shared" si="5"/>
-        <v>-2.8116592607485558E-6</v>
+        <v>2.8116592607485558E-6</v>
       </c>
       <c r="E87" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9596413269722699E-6</v>
+        <v>2.9596413269722699E-6</v>
       </c>
       <c r="F87" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9596413271037434E-6</v>
+        <v>2.9596413271037434E-6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2630,15 +2630,15 @@
       </c>
       <c r="D88">
         <f t="shared" si="5"/>
-        <v>-2.8450688213110809E-6</v>
+        <v>2.8450688213110809E-6</v>
       </c>
       <c r="E88" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9636133555540609E-6</v>
+        <v>2.9636133555540609E-6</v>
       </c>
       <c r="F88" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9636133555323769E-6</v>
+        <v>2.9636133555323769E-6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2654,15 +2654,15 @@
       </c>
       <c r="D89">
         <f t="shared" si="5"/>
-        <v>-2.8784783842050743E-6</v>
+        <v>2.8784783842050743E-6</v>
       </c>
       <c r="E89" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9675034889642072E-6</v>
+        <v>2.9675034889642072E-6</v>
       </c>
       <c r="F89" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9675034888712118E-6</v>
+        <v>2.9675034888712118E-6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2678,15 +2678,15 @@
       </c>
       <c r="D90">
         <f t="shared" si="5"/>
-        <v>-2.9118879475431569E-6</v>
+        <v>2.9118879475431569E-6</v>
       </c>
       <c r="E90" s="1">
         <f t="shared" si="6"/>
-        <v>-2.9713142320736078E-6</v>
+        <v>2.9713142320736078E-6</v>
       </c>
       <c r="F90" s="1">
         <f t="shared" si="7"/>
-        <v>-2.9713142321868959E-6</v>
+        <v>2.9713142321868959E-6</v>
       </c>
     </row>
   </sheetData>
